--- a/data/trans_orig/IP36A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP36A-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>17460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25424</t>
+          <t>25264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32112</t>
+          <t>32064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21591</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19343</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42712</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28351</t>
+          <t>28309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>43709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11803</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>17214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63978</t>
+          <t>63126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71163</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65513</t>
+          <t>66270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74046</t>
+          <t>74132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>133171</t>
+          <t>133523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>143975</t>
+          <t>143851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49366</t>
+          <t>49133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55776</t>
+          <t>55461</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53681</t>
+          <t>53820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59374</t>
+          <t>59277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104923</t>
+          <t>105477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113837</t>
+          <t>113930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59690</t>
+          <t>59339</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67473</t>
+          <t>67410</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60787</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68334</t>
+          <t>68483</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124701</t>
+          <t>123523</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134232</t>
+          <t>134081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14245</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32779</t>
+          <t>32497</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>53213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230050</t>
+          <t>230875</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245206</t>
+          <t>245078</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>248836</t>
+          <t>249902</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>263015</t>
+          <t>262961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>484884</t>
+          <t>484370</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>504804</t>
+          <t>505086</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35803</t>
+          <t>35634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41762</t>
+          <t>41765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>12997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29671</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31197</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37918</t>
+          <t>37908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63958</t>
+          <t>63695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72683</t>
+          <t>72573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21972</t>
+          <t>22367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28619</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31535</t>
+          <t>31678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38911</t>
+          <t>38750</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>56758</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66341</t>
+          <t>65927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21940</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23107</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40141</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96349</t>
+          <t>95723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108280</t>
+          <t>107882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99573</t>
+          <t>99924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111913</t>
+          <t>111833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>200104</t>
+          <t>198829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217138</t>
+          <t>216869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>16263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>15762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80376</t>
+          <t>79811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90005</t>
+          <t>90057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74711</t>
+          <t>74791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85124</t>
+          <t>84771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>158436</t>
+          <t>159562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173250</t>
+          <t>172921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>40868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55094</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62036</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99314</t>
+          <t>98798</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107491</t>
+          <t>107392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46899</t>
+          <t>46856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>51266</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65864</t>
+          <t>64482</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92866</t>
+          <t>91443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>304456</t>
+          <t>304499</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>323277</t>
+          <t>322723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325233</t>
+          <t>326529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346093</t>
+          <t>345695</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>636284</t>
+          <t>637707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>664668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>19789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38573</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36481</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63687</t>
+          <t>63376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73505</t>
+          <t>73584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25510</t>
+          <t>25265</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35270</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44152</t>
+          <t>44063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>20631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36270</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91306</t>
+          <t>91343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101558</t>
+          <t>101526</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74101</t>
+          <t>72903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85562</t>
+          <t>85117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>168219</t>
+          <t>168280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184074</t>
+          <t>183858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>22175</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71116</t>
+          <t>71247</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78477</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69329</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79028</t>
+          <t>78595</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143606</t>
+          <t>143489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155333</t>
+          <t>155873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51219</t>
+          <t>50447</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>56754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>63506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110314</t>
+          <t>110480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118061</t>
+          <t>117729</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>37222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33439</t>
+          <t>33881</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>54111</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59976</t>
+          <t>58655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85512</t>
+          <t>85346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>288563</t>
+          <t>288237</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>304023</t>
+          <t>304728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278199</t>
+          <t>277976</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>298648</t>
+          <t>298206</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>572034</t>
+          <t>572200</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>597570</t>
+          <t>598891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>20661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34472</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18796</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16663</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>25896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34453</t>
+          <t>34247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>26021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>23832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>78156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89742</t>
+          <t>90119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>54356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64222</t>
+          <t>63962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137267</t>
+          <t>137244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152267</t>
+          <t>152983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24587</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>22613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24919</t>
+          <t>25221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43408</t>
+          <t>43461</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>26418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40106</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34698</t>
+          <t>35228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46553</t>
+          <t>46901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65288</t>
+          <t>65235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83777</t>
+          <t>83475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51214</t>
+          <t>50037</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61286</t>
+          <t>61177</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55410</t>
+          <t>54650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>63844</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109226</t>
+          <t>109611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>123336</t>
+          <t>123394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,91%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>28373</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>55325</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36394</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58139</t>
+          <t>58387</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69789</t>
+          <t>69229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106073</t>
+          <t>105111</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>200055</t>
+          <t>201753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>228359</t>
+          <t>228705</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>193172</t>
+          <t>192924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>214917</t>
+          <t>215935</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>402316</t>
+          <t>403278</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>438600</t>
+          <t>439160</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
